--- a/docs/migration/almiras-migration-workbook.xlsx
+++ b/docs/migration/almiras-migration-workbook.xlsx
@@ -44,7 +44,7 @@
     <definedName name="L_checklist_status">'Lists'!$R$2:$R$4</definedName>
     <definedName name="L_currency">'Lists'!$S$2:$S$18</definedName>
     <definedName name="L_country">'Lists'!$T$2:$T$250</definedName>
-    <definedName name="L_erp_code">'Lists'!$U$2:$U$64</definedName>
+    <definedName name="L_erp_code">'Lists'!$U$2:$U$69</definedName>
     <definedName name="L_entity">'Entities'!$A$6:$A$2005</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3179,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3587,17 +3587,17 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sharia-compliant deposits (e.g. murabaha, wakala)</t>
+          <t>Employee loans and advances</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>ودائع متوافقة مع الشريعة</t>
+          <t>قروض وسلف الموظفين</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3629,17 +3629,17 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VAT input</t>
+          <t>Employee deferred-sale (bai' ajel) receivable</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>ضريبة القيمة المضافة - مدخلات</t>
+          <t>ذمم البيع الآجل للموظفين</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3671,17 +3671,17 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prepayments</t>
+          <t>Sharia-compliant deposits (e.g. murabaha, wakala)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>مصروفات مدفوعة مقدماً</t>
+          <t>ودائع متوافقة مع الشريعة</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Investments in subsidiaries</t>
+          <t>VAT input</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>استثمارات في شركات تابعة</t>
+          <t>ضريبة القيمة المضافة - مدخلات</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3755,17 +3755,17 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Investments in associates (equity method)</t>
+          <t>Prepayments</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>استثمارات في شركات زميلة</t>
+          <t>مصروفات مدفوعة مقدماً</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3797,17 +3797,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other equity investments</t>
+          <t>Investments in subsidiaries</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>استثمارات حقوق ملكية أخرى</t>
+          <t>استثمارات في شركات تابعة</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3839,17 +3839,17 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Investments in associates (equity method)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>الممتلكات والآلات والمعدات</t>
+          <t>استثمارات في شركات زميلة</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3881,17 +3881,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Investment property (rental assets)</t>
+          <t>Other equity investments</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>عقارات استثمارية</t>
+          <t>استثمارات حقوق ملكية أخرى</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3923,17 +3923,17 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vehicles</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>السيارات</t>
+          <t>الممتلكات والآلات والمعدات</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3965,17 +3965,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Accumulated depreciation</t>
+          <t>Investment property (rental assets)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>مجمع الاستهلاك</t>
+          <t>عقارات استثمارية</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4007,17 +4007,17 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Intangible assets and IP</t>
+          <t>Vehicles</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>الأصول غير الملموسة والملكية الفكرية</t>
+          <t>السيارات</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4049,27 +4049,27 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Accumulated depreciation</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>الالتزامات</t>
+          <t>مجمع الاستهلاك</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>liability</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4091,22 +4091,22 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trade payables</t>
+          <t>Intangible assets and IP</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>الذمم الدائنة التجارية</t>
+          <t>الأصول غير الملموسة والملكية الفكرية</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>liability</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4126,24 +4126,24 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Due to group entities</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>مستحق لشركات المجموعة</t>
+          <t>الالتزامات</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4168,24 +4168,24 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VAT output</t>
+          <t>Trade payables</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>ضريبة القيمة المضافة - مخرجات</t>
+          <t>الذمم الدائنة التجارية</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4210,24 +4210,24 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Zakat payable</t>
+          <t>Due to group entities</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>الزكاة المستحقة</t>
+          <t>مستحق لشركات المجموعة</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4252,24 +4252,24 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Withholding tax payable</t>
+          <t>VAT output</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ضريبة الاستقطاع المستحقة</t>
+          <t>ضريبة القيمة المضافة - مخرجات</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4301,17 +4301,17 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Accrued expenses</t>
+          <t>Zakat payable</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>مصروفات مستحقة</t>
+          <t>الزكاة المستحقة</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4343,17 +4343,17 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Islamic financing (murabaha, tawarruq)</t>
+          <t>Withholding tax payable</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>تمويل إسلامي</t>
+          <t>ضريبة الاستقطاع المستحقة</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4385,17 +4385,17 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Conventional interest-bearing loans</t>
+          <t>Accrued expenses</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>قروض تقليدية بفائدة</t>
+          <t>مصروفات مستحقة</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4427,17 +4427,17 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>End-of-service provision</t>
+          <t>Salaries payable</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>مخصص مكافأة نهاية الخدمة</t>
+          <t>رواتب مستحقة</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4469,17 +4469,17 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Charity payable (purification)</t>
+          <t>GOSI payable</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>مبالغ مستحقة للتطهير</t>
+          <t>اشتراكات التأمينات الاجتماعية المستحقة</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4511,27 +4511,27 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Islamic financing (murabaha, tawarruq)</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>حقوق الملكية</t>
+          <t>تمويل إسلامي</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>liability</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4553,22 +4553,22 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Conventional interest-bearing loans</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>رأس المال</t>
+          <t>قروض تقليدية بفائدة</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>liability</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4595,22 +4595,22 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Statutory reserve</t>
+          <t>End-of-service provision</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>الاحتياطي النظامي</t>
+          <t>مخصص مكافأة نهاية الخدمة</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>liability</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4637,22 +4637,22 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Retained earnings</t>
+          <t>Charity payable (purification)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>الأرباح المبقاة</t>
+          <t>مبالغ مستحقة للتطهير</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>liability</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4679,17 +4679,17 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Foreign currency translation reserve</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>احتياطي ترجمة العملات الأجنبية</t>
+          <t>حقوق الملكية</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4721,17 +4721,17 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Opening balance equity (migration)</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>حقوق ملكية الأرصدة الافتتاحية</t>
+          <t>رأس المال</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4763,27 +4763,27 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Statutory reserve</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>الإيرادات</t>
+          <t>الاحتياطي النظامي</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4805,22 +4805,22 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rental income</t>
+          <t>Retained earnings</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>إيرادات الإيجار</t>
+          <t>الأرباح المبقاة</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4847,27 +4847,27 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Intercompany rental income</t>
+          <t>Foreign currency translation reserve</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>إيرادات إيجار من شركات المجموعة</t>
+          <t>احتياطي ترجمة العملات الأجنبية</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4889,22 +4889,22 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Residential rental income (VAT-exempt)</t>
+          <t>Opening balance equity (migration)</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>إيرادات الإيجار السكني (معفاة)</t>
+          <t>حقوق ملكية الأرصدة الافتتاحية</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4931,17 +4931,17 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Secondment and consulting income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>إيرادات الإعارة والاستشارات</t>
+          <t>الإيرادات</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4973,17 +4973,17 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intercompany service income</t>
+          <t>Rental income</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>إيرادات خدمات من شركات المجموعة</t>
+          <t>إيرادات الإيجار</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5015,17 +5015,17 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Management fee income</t>
+          <t>Intercompany rental income</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>إيرادات رسوم الإدارة</t>
+          <t>إيرادات إيجار من شركات المجموعة</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5057,17 +5057,17 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Service charge income</t>
+          <t>Residential rental income (VAT-exempt)</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>إيرادات رسوم الخدمات المشتركة</t>
+          <t>إيرادات الإيجار السكني (معفاة)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5099,17 +5099,17 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Service fee income</t>
+          <t>Secondment and consulting income</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>إيرادات أتعاب الخدمات</t>
+          <t>إيرادات الإعارة والاستشارات</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5141,17 +5141,17 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>IP and licence income</t>
+          <t>Intercompany service income</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>إيرادات الملكية الفكرية والتراخيص</t>
+          <t>إيرادات خدمات من شركات المجموعة</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5183,17 +5183,17 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intercompany IP and licence income</t>
+          <t>Management fee income</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>إيرادات ملكية فكرية من شركات المجموعة</t>
+          <t>إيرادات رسوم الإدارة</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5225,17 +5225,17 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dividend income</t>
+          <t>Service charge income</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>إيرادات توزيعات الأرباح</t>
+          <t>إيرادات رسوم الخدمات المشتركة</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5267,17 +5267,17 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Share of profit of associates</t>
+          <t>Service fee income</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>الحصة من أرباح الشركات الزميلة</t>
+          <t>إيرادات أتعاب الخدمات</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5309,17 +5309,17 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Islamic deposit profit</t>
+          <t>IP and licence income</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>أرباح الودائع الإسلامية</t>
+          <t>إيرادات الملكية الفكرية والتراخيص</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5351,17 +5351,17 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Foreign exchange gain – realised</t>
+          <t>Intercompany IP and licence income</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>أرباح فروقات العملة المحققة</t>
+          <t>إيرادات ملكية فكرية من شركات المجموعة</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5393,17 +5393,17 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Foreign exchange gain – unrealised</t>
+          <t>Dividend income</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>أرباح فروقات العملة غير المحققة</t>
+          <t>إيرادات توزيعات الأرباح</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5435,17 +5435,17 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Non-compliant income (to purify)</t>
+          <t>Share of profit of associates</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>إيرادات غير متوافقة (للتطهير)</t>
+          <t>الحصة من أرباح الشركات الزميلة</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5477,27 +5477,27 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Islamic deposit profit</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>المصروفات</t>
+          <t>أرباح الودائع الإسلامية</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>expense</t>
+          <t>income</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5519,22 +5519,22 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
+          <t>Foreign exchange gain – realised</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>الرواتب والمزايا</t>
+          <t>أرباح فروقات العملة المحققة</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>expense</t>
+          <t>income</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5561,22 +5561,22 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GOSI</t>
+          <t>Foreign exchange gain – unrealised</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>التأمينات الاجتماعية</t>
+          <t>أرباح فروقات العملة غير المحققة</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>expense</t>
+          <t>income</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5603,22 +5603,22 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Non-compliant income (to purify)</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>الإيجار</t>
+          <t>إيرادات غير متوافقة (للتطهير)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>expense</t>
+          <t>income</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5645,17 +5645,17 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>الأتعاب المهنية</t>
+          <t>المصروفات</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5687,17 +5687,17 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Salaries and benefits</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>الاستهلاك</t>
+          <t>الرواتب والمزايا</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5729,17 +5729,17 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Repairs and maintenance</t>
+          <t>GOSI</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>الإصلاح والصيانة</t>
+          <t>التأمينات الاجتماعية</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5771,17 +5771,17 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vehicle fuel and running costs</t>
+          <t>End-of-service benefit expense</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>وقود ومصروفات السيارات</t>
+          <t>مصروف مكافأة نهاية الخدمة</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5813,17 +5813,17 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Islamic financing cost</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>تكلفة التمويل الإسلامي</t>
+          <t>الإيجار</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5855,17 +5855,17 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Conventional interest expense</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>مصروف فوائد تقليدية</t>
+          <t>الأتعاب المهنية</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5897,17 +5897,17 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>رسوم بنكية</t>
+          <t>الاستهلاك</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5939,17 +5939,17 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Foreign exchange loss – realised</t>
+          <t>Repairs and maintenance</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>خسائر فروقات العملة المحققة</t>
+          <t>الإصلاح والصيانة</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5981,17 +5981,17 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Foreign exchange loss – unrealised</t>
+          <t>Vehicle fuel and running costs</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>خسائر فروقات العملة غير المحققة</t>
+          <t>وقود ومصروفات السيارات</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6023,17 +6023,17 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Currency rounding differences</t>
+          <t>Islamic financing cost</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>فروقات تقريب العملات</t>
+          <t>تكلفة التمويل الإسلامي</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6065,17 +6065,17 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Zakat</t>
+          <t>Conventional interest expense</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>الزكاة</t>
+          <t>مصروف فوائد تقليدية</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6107,17 +6107,17 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>مصروفات عمومية وإدارية</t>
+          <t>رسوم بنكية</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6149,40 +6149,250 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
+          <t>5750</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss – realised</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>خسائر فروقات العملة المحققة</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Yes / نعم</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>5760</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss – unrealised</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>خسائر فروقات العملة غير المحققة</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Yes / نعم</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>5770</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Currency rounding differences</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>فروقات تقريب العملات</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Yes / نعم</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>5800</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Zakat</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>الزكاة</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Yes / نعم</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>5900</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>مصروفات عمومية وإدارية</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Yes / نعم</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
           <t>5920</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>Withholding tax borne (gross-up)</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>ضريبة استقطاع محملة على الشركة</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>expense</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Yes / نعم</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>No / لا</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>No / لا</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t>No / لا</t>
         </is>
@@ -6767,7 +6977,7 @@
       </c>
       <c r="U8" s="6" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1230</t>
         </is>
       </c>
     </row>
@@ -6794,7 +7004,7 @@
       </c>
       <c r="U9" s="6" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1240</t>
         </is>
       </c>
     </row>
@@ -6821,7 +7031,7 @@
       </c>
       <c r="U10" s="6" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1300</t>
         </is>
       </c>
     </row>
@@ -6848,7 +7058,7 @@
       </c>
       <c r="U11" s="6" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1310</t>
         </is>
       </c>
     </row>
@@ -6875,7 +7085,7 @@
       </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1320</t>
         </is>
       </c>
     </row>
@@ -6892,7 +7102,7 @@
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1400</t>
         </is>
       </c>
     </row>
@@ -6909,7 +7119,7 @@
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1410</t>
         </is>
       </c>
     </row>
@@ -6926,7 +7136,7 @@
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1420</t>
         </is>
       </c>
     </row>
@@ -6943,7 +7153,7 @@
       </c>
       <c r="U16" s="6" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1500</t>
         </is>
       </c>
     </row>
@@ -6960,7 +7170,7 @@
       </c>
       <c r="U17" s="6" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1510</t>
         </is>
       </c>
     </row>
@@ -6977,7 +7187,7 @@
       </c>
       <c r="U18" s="6" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1520</t>
         </is>
       </c>
     </row>
@@ -6989,7 +7199,7 @@
       </c>
       <c r="U19" s="6" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1590</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7211,7 @@
       </c>
       <c r="U20" s="6" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>1600</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7223,7 @@
       </c>
       <c r="U21" s="6" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
     </row>
@@ -7025,7 +7235,7 @@
       </c>
       <c r="U22" s="6" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2110</t>
         </is>
       </c>
     </row>
@@ -7037,7 +7247,7 @@
       </c>
       <c r="U23" s="6" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2200</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7259,7 @@
       </c>
       <c r="U24" s="6" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2210</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7271,7 @@
       </c>
       <c r="U25" s="6" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2220</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7283,7 @@
       </c>
       <c r="U26" s="6" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2300</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7295,7 @@
       </c>
       <c r="U27" s="6" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2330</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7307,7 @@
       </c>
       <c r="U28" s="6" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2340</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7319,7 @@
       </c>
       <c r="U29" s="6" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2400</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7331,7 @@
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2410</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7343,7 @@
       </c>
       <c r="U31" s="6" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>2500</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7355,7 @@
       </c>
       <c r="U32" s="6" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>2600</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7367,7 @@
       </c>
       <c r="U33" s="6" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3100</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7379,7 @@
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>3200</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7391,7 @@
       </c>
       <c r="U35" s="6" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>3300</t>
         </is>
       </c>
     </row>
@@ -7193,7 +7403,7 @@
       </c>
       <c r="U36" s="6" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>3900</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7415,7 @@
       </c>
       <c r="U37" s="6" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4100</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7427,7 @@
       </c>
       <c r="U38" s="6" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4110</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7439,7 @@
       </c>
       <c r="U39" s="6" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4120</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7451,7 @@
       </c>
       <c r="U40" s="6" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4200</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7463,7 @@
       </c>
       <c r="U41" s="6" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4210</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7475,7 @@
       </c>
       <c r="U42" s="6" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4220</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7487,7 @@
       </c>
       <c r="U43" s="6" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4230</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7499,7 @@
       </c>
       <c r="U44" s="6" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4240</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7511,7 @@
       </c>
       <c r="U45" s="6" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4300</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7523,7 @@
       </c>
       <c r="U46" s="6" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4310</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7535,7 @@
       </c>
       <c r="U47" s="6" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4400</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7547,7 @@
       </c>
       <c r="U48" s="6" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4500</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7559,7 @@
       </c>
       <c r="U49" s="6" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4600</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7571,7 @@
       </c>
       <c r="U50" s="6" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4700</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7583,7 @@
       </c>
       <c r="U51" s="6" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4710</t>
         </is>
       </c>
     </row>
@@ -7385,7 +7595,7 @@
       </c>
       <c r="U52" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>4900</t>
         </is>
       </c>
     </row>
@@ -7397,7 +7607,7 @@
       </c>
       <c r="U53" s="6" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5100</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7619,7 @@
       </c>
       <c r="U54" s="6" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5110</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7631,7 @@
       </c>
       <c r="U55" s="6" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5120</t>
         </is>
       </c>
     </row>
@@ -7433,7 +7643,7 @@
       </c>
       <c r="U56" s="6" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5200</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7655,7 @@
       </c>
       <c r="U57" s="6" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5300</t>
         </is>
       </c>
     </row>
@@ -7457,7 +7667,7 @@
       </c>
       <c r="U58" s="6" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5400</t>
         </is>
       </c>
     </row>
@@ -7469,7 +7679,7 @@
       </c>
       <c r="U59" s="6" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5500</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7691,7 @@
       </c>
       <c r="U60" s="6" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5510</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7703,7 @@
       </c>
       <c r="U61" s="6" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5600</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7715,7 @@
       </c>
       <c r="U62" s="6" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5610</t>
         </is>
       </c>
     </row>
@@ -7517,7 +7727,7 @@
       </c>
       <c r="U63" s="6" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5700</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7739,7 @@
       </c>
       <c r="U64" s="6" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5750</t>
         </is>
       </c>
     </row>
@@ -7539,6 +7749,11 @@
           <t>EE</t>
         </is>
       </c>
+      <c r="U65" s="6" t="inlineStr">
+        <is>
+          <t>5760</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="T66" s="6" t="inlineStr">
@@ -7546,6 +7761,11 @@
           <t>EG</t>
         </is>
       </c>
+      <c r="U66" s="6" t="inlineStr">
+        <is>
+          <t>5770</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="T67" s="6" t="inlineStr">
@@ -7553,6 +7773,11 @@
           <t>EH</t>
         </is>
       </c>
+      <c r="U67" s="6" t="inlineStr">
+        <is>
+          <t>5800</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="T68" s="6" t="inlineStr">
@@ -7560,11 +7785,21 @@
           <t>ER</t>
         </is>
       </c>
+      <c r="U68" s="6" t="inlineStr">
+        <is>
+          <t>5900</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="T69" s="6" t="inlineStr">
         <is>
           <t>ES</t>
+        </is>
+      </c>
+      <c r="U69" s="6" t="inlineStr">
+        <is>
+          <t>5920</t>
         </is>
       </c>
     </row>

--- a/docs/migration/almiras-migration-workbook.xlsx
+++ b/docs/migration/almiras-migration-workbook.xlsx
@@ -44,7 +44,7 @@
     <definedName name="L_checklist_status">'Lists'!$R$2:$R$4</definedName>
     <definedName name="L_currency">'Lists'!$S$2:$S$18</definedName>
     <definedName name="L_country">'Lists'!$T$2:$T$250</definedName>
-    <definedName name="L_erp_code">'Lists'!$U$2:$U$69</definedName>
+    <definedName name="L_erp_code">'Lists'!$U$2:$U$73</definedName>
     <definedName name="L_entity">'Entities'!$A$6:$A$2005</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3179,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3671,17 +3671,17 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sharia-compliant deposits (e.g. murabaha, wakala)</t>
+          <t>Deferred bai' ajel profit (contra 1240)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>ودائع متوافقة مع الشريعة</t>
+          <t>أرباح البيع الآجل المؤجلة</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VAT input</t>
+          <t>Assets acquired for employee deferred sale</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ضريبة القيمة المضافة - مدخلات</t>
+          <t>أصول مشتراة للبيع الآجل للموظفين</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3755,17 +3755,17 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prepayments</t>
+          <t>Sharia-compliant deposits (e.g. murabaha, wakala)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>مصروفات مدفوعة مقدماً</t>
+          <t>ودائع متوافقة مع الشريعة</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3797,17 +3797,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Investments in subsidiaries</t>
+          <t>VAT input</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>استثمارات في شركات تابعة</t>
+          <t>ضريبة القيمة المضافة - مدخلات</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3839,17 +3839,17 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Investments in associates (equity method)</t>
+          <t>Prepayments</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>استثمارات في شركات زميلة</t>
+          <t>مصروفات مدفوعة مقدماً</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3881,17 +3881,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Other equity investments</t>
+          <t>Investments in subsidiaries</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>استثمارات حقوق ملكية أخرى</t>
+          <t>استثمارات في شركات تابعة</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3923,17 +3923,17 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Investments in associates (equity method)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>الممتلكات والآلات والمعدات</t>
+          <t>استثمارات في شركات زميلة</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3965,17 +3965,17 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Investment property (rental assets)</t>
+          <t>Other equity investments</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>عقارات استثمارية</t>
+          <t>استثمارات حقوق ملكية أخرى</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4007,17 +4007,17 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vehicles</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>السيارات</t>
+          <t>الممتلكات والآلات والمعدات</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4049,17 +4049,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Accumulated depreciation</t>
+          <t>Investment property (rental assets)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>مجمع الاستهلاك</t>
+          <t>عقارات استثمارية</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4091,17 +4091,17 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Intangible assets and IP</t>
+          <t>Vehicles</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>الأصول غير الملموسة والملكية الفكرية</t>
+          <t>السيارات</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4133,27 +4133,27 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Accumulated depreciation</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>الالتزامات</t>
+          <t>مجمع الاستهلاك</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>liability</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4175,22 +4175,22 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trade payables</t>
+          <t>Intangible assets and IP</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>الذمم الدائنة التجارية</t>
+          <t>الأصول غير الملموسة والملكية الفكرية</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>liability</t>
+          <t>asset</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4210,24 +4210,24 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Due to group entities</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>مستحق لشركات المجموعة</t>
+          <t>الالتزامات</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4252,24 +4252,24 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VAT output</t>
+          <t>Trade payables</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ضريبة القيمة المضافة - مخرجات</t>
+          <t>الذمم الدائنة التجارية</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4294,24 +4294,24 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zakat payable</t>
+          <t>Due to group entities</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>الزكاة المستحقة</t>
+          <t>مستحق لشركات المجموعة</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4336,24 +4336,24 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Withholding tax payable</t>
+          <t>VAT output</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ضريبة الاستقطاع المستحقة</t>
+          <t>ضريبة القيمة المضافة - مخرجات</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4385,17 +4385,17 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Accrued expenses</t>
+          <t>Zakat payable</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>مصروفات مستحقة</t>
+          <t>الزكاة المستحقة</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4427,17 +4427,17 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Salaries payable</t>
+          <t>Withholding tax payable</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>رواتب مستحقة</t>
+          <t>ضريبة الاستقطاع المستحقة</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4469,17 +4469,17 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GOSI payable</t>
+          <t>Accrued expenses</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>اشتراكات التأمينات الاجتماعية المستحقة</t>
+          <t>مصروفات مستحقة</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4511,17 +4511,17 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Islamic financing (murabaha, tawarruq)</t>
+          <t>Salaries payable</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>تمويل إسلامي</t>
+          <t>رواتب مستحقة</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4553,17 +4553,17 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Conventional interest-bearing loans</t>
+          <t>GOSI payable</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>قروض تقليدية بفائدة</t>
+          <t>اشتراكات التأمينات الاجتماعية المستحقة</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4595,17 +4595,17 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>End-of-service provision</t>
+          <t>Islamic financing (murabaha, tawarruq)</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>مخصص مكافأة نهاية الخدمة</t>
+          <t>تمويل إسلامي</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4637,17 +4637,17 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Charity payable (purification)</t>
+          <t>Conventional interest-bearing loans</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>مبالغ مستحقة للتطهير</t>
+          <t>قروض تقليدية بفائدة</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4679,27 +4679,27 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>End-of-service provision</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>حقوق الملكية</t>
+          <t>مخصص مكافأة نهاية الخدمة</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>liability</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4721,22 +4721,22 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Share capital</t>
+          <t>Charity payable (purification)</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>رأس المال</t>
+          <t>مبالغ مستحقة للتطهير</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>equity</t>
+          <t>liability</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4763,17 +4763,17 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Statutory reserve</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>الاحتياطي النظامي</t>
+          <t>حقوق الملكية</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4805,17 +4805,17 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Retained earnings</t>
+          <t>Share capital</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>الأرباح المبقاة</t>
+          <t>رأس المال</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4847,17 +4847,17 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Foreign currency translation reserve</t>
+          <t>Statutory reserve</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>احتياطي ترجمة العملات الأجنبية</t>
+          <t>الاحتياطي النظامي</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4889,17 +4889,17 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Opening balance equity (migration)</t>
+          <t>Retained earnings</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>حقوق ملكية الأرصدة الافتتاحية</t>
+          <t>الأرباح المبقاة</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4931,22 +4931,22 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Foreign currency translation reserve</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>الإيرادات</t>
+          <t>احتياطي ترجمة العملات الأجنبية</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4973,22 +4973,22 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rental income</t>
+          <t>Opening balance equity (migration)</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>إيرادات الإيجار</t>
+          <t>حقوق ملكية الأرصدة الافتتاحية</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>equity</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5015,17 +5015,17 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Intercompany rental income</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>إيرادات إيجار من شركات المجموعة</t>
+          <t>الإيرادات</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5057,17 +5057,17 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Residential rental income (VAT-exempt)</t>
+          <t>Rental income</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>إيرادات الإيجار السكني (معفاة)</t>
+          <t>إيرادات الإيجار</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5099,17 +5099,17 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Secondment and consulting income</t>
+          <t>Intercompany rental income</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>إيرادات الإعارة والاستشارات</t>
+          <t>إيرادات إيجار من شركات المجموعة</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5141,17 +5141,17 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Intercompany service income</t>
+          <t>Residential rental income (VAT-exempt)</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>إيرادات خدمات من شركات المجموعة</t>
+          <t>إيرادات الإيجار السكني (معفاة)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5183,17 +5183,17 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Management fee income</t>
+          <t>Secondment and consulting income</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>إيرادات رسوم الإدارة</t>
+          <t>إيرادات الإعارة والاستشارات</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5225,17 +5225,17 @@
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Service charge income</t>
+          <t>Intercompany service income</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>إيرادات رسوم الخدمات المشتركة</t>
+          <t>إيرادات خدمات من شركات المجموعة</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5267,17 +5267,17 @@
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Service fee income</t>
+          <t>Management fee income</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>إيرادات أتعاب الخدمات</t>
+          <t>إيرادات رسوم الإدارة</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5309,17 +5309,17 @@
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>IP and licence income</t>
+          <t>Service charge income</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>إيرادات الملكية الفكرية والتراخيص</t>
+          <t>إيرادات رسوم الخدمات المشتركة</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5351,17 +5351,17 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Intercompany IP and licence income</t>
+          <t>Service fee income</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>إيرادات ملكية فكرية من شركات المجموعة</t>
+          <t>إيرادات أتعاب الخدمات</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5393,17 +5393,17 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dividend income</t>
+          <t>IP and licence income</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>إيرادات توزيعات الأرباح</t>
+          <t>إيرادات الملكية الفكرية والتراخيص</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5435,17 +5435,17 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Share of profit of associates</t>
+          <t>Intercompany IP and licence income</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>الحصة من أرباح الشركات الزميلة</t>
+          <t>إيرادات ملكية فكرية من شركات المجموعة</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5477,17 +5477,17 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Islamic deposit profit</t>
+          <t>Dividend income</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>أرباح الودائع الإسلامية</t>
+          <t>إيرادات توزيعات الأرباح</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5519,17 +5519,17 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Foreign exchange gain – realised</t>
+          <t>Share of profit of associates</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>أرباح فروقات العملة المحققة</t>
+          <t>الحصة من أرباح الشركات الزميلة</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5561,17 +5561,17 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Foreign exchange gain – unrealised</t>
+          <t>Islamic deposit profit</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>أرباح فروقات العملة غير المحققة</t>
+          <t>أرباح الودائع الإسلامية</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5603,17 +5603,17 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Non-compliant income (to purify)</t>
+          <t>Bai' ajel profit income</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>إيرادات غير متوافقة (للتطهير)</t>
+          <t>إيرادات أرباح البيع الآجل</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5645,27 +5645,27 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Foreign exchange gain – realised</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>المصروفات</t>
+          <t>أرباح فروقات العملة المحققة</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>expense</t>
+          <t>income</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5687,22 +5687,22 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Salaries and benefits</t>
+          <t>Foreign exchange gain – unrealised</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>الرواتب والمزايا</t>
+          <t>أرباح فروقات العملة غير المحققة</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>expense</t>
+          <t>income</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5729,22 +5729,22 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GOSI</t>
+          <t>Non-compliant income (to purify)</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>التأمينات الاجتماعية</t>
+          <t>إيرادات غير متوافقة (للتطهير)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>expense</t>
+          <t>income</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5771,17 +5771,17 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>End-of-service benefit expense</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>مصروف مكافأة نهاية الخدمة</t>
+          <t>المصروفات</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5813,17 +5813,17 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>Salaries and benefits</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>الإيجار</t>
+          <t>الرواتب والمزايا</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5855,17 +5855,17 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>GOSI</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>الأتعاب المهنية</t>
+          <t>التأمينات الاجتماعية</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5897,17 +5897,17 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>End-of-service benefit expense</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>الاستهلاك</t>
+          <t>مصروف مكافأة نهاية الخدمة</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5939,17 +5939,17 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Repairs and maintenance</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>الإصلاح والصيانة</t>
+          <t>الإيجار</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5981,17 +5981,17 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Vehicle fuel and running costs</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>وقود ومصروفات السيارات</t>
+          <t>الأتعاب المهنية</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6023,17 +6023,17 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Islamic financing cost</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>تكلفة التمويل الإسلامي</t>
+          <t>الاستهلاك</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6065,17 +6065,17 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Conventional interest expense</t>
+          <t>Repairs and maintenance</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>مصروف فوائد تقليدية</t>
+          <t>الإصلاح والصيانة</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Yes / نعم</t>
+          <t>No / لا</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6107,17 +6107,17 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Vehicle fuel and running costs</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>رسوم بنكية</t>
+          <t>وقود ومصروفات السيارات</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6149,17 +6149,17 @@
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Foreign exchange loss – realised</t>
+          <t>Islamic financing cost</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>خسائر فروقات العملة المحققة</t>
+          <t>تكلفة التمويل الإسلامي</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6191,17 +6191,17 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Foreign exchange loss – unrealised</t>
+          <t>Conventional interest expense</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>خسائر فروقات العملة غير المحققة</t>
+          <t>مصروف فوائد تقليدية</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>No / لا</t>
+          <t>Yes / نعم</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6233,17 +6233,17 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Currency rounding differences</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>فروقات تقريب العملات</t>
+          <t>رسوم بنكية</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6275,17 +6275,17 @@
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5750</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Zakat</t>
+          <t>Foreign exchange loss – realised</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>الزكاة</t>
+          <t>خسائر فروقات العملة المحققة</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6317,17 +6317,17 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>General and administrative</t>
+          <t>Foreign exchange loss – unrealised</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>مصروفات عمومية وإدارية</t>
+          <t>خسائر فروقات العملة غير المحققة</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6359,40 +6359,208 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
+          <t>5770</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Currency rounding differences</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>فروقات تقريب العملات</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Yes / نعم</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>5800</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Zakat</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>الزكاة</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Yes / نعم</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>5900</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>مصروفات عمومية وإدارية</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Yes / نعم</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
           <t>5920</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>Withholding tax borne (gross-up)</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>ضريبة استقطاع محملة على الشركة</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>expense</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Yes / نعم</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>No / لا</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>No / لا</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>5930</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>GOSI late-payment fines</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>غرامات تأخير التأمينات</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>expense</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Yes / نعم</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>No / لا</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t>No / لا</t>
         </is>
@@ -7031,7 +7199,7 @@
       </c>
       <c r="U10" s="6" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1241</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7226,7 @@
       </c>
       <c r="U11" s="6" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1250</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7253,7 @@
       </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1300</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7270,7 @@
       </c>
       <c r="U13" s="6" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1310</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7287,7 @@
       </c>
       <c r="U14" s="6" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1320</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7304,7 @@
       </c>
       <c r="U15" s="6" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1400</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7321,7 @@
       </c>
       <c r="U16" s="6" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1410</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7338,7 @@
       </c>
       <c r="U17" s="6" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>1420</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7355,7 @@
       </c>
       <c r="U18" s="6" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1500</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7367,7 @@
       </c>
       <c r="U19" s="6" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1510</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7379,7 @@
       </c>
       <c r="U20" s="6" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1520</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7391,7 @@
       </c>
       <c r="U21" s="6" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1590</t>
         </is>
       </c>
     </row>
@@ -7235,7 +7403,7 @@
       </c>
       <c r="U22" s="6" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>1600</t>
         </is>
       </c>
     </row>
@@ -7247,7 +7415,7 @@
       </c>
       <c r="U23" s="6" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2100</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7427,7 @@
       </c>
       <c r="U24" s="6" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2110</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7439,7 @@
       </c>
       <c r="U25" s="6" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2200</t>
         </is>
       </c>
     </row>
@@ -7283,7 +7451,7 @@
       </c>
       <c r="U26" s="6" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2210</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7463,7 @@
       </c>
       <c r="U27" s="6" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2220</t>
         </is>
       </c>
     </row>
@@ -7307,7 +7475,7 @@
       </c>
       <c r="U28" s="6" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2300</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7487,7 @@
       </c>
       <c r="U29" s="6" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2330</t>
         </is>
       </c>
     </row>
@@ -7331,7 +7499,7 @@
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2340</t>
         </is>
       </c>
     </row>
@@ -7343,7 +7511,7 @@
       </c>
       <c r="U31" s="6" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2400</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7523,7 @@
       </c>
       <c r="U32" s="6" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2410</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7535,7 @@
       </c>
       <c r="U33" s="6" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2500</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7547,7 @@
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2600</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7559,7 @@
       </c>
       <c r="U35" s="6" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3100</t>
         </is>
       </c>
     </row>
@@ -7403,7 +7571,7 @@
       </c>
       <c r="U36" s="6" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>3200</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7583,7 @@
       </c>
       <c r="U37" s="6" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3300</t>
         </is>
       </c>
     </row>
@@ -7427,7 +7595,7 @@
       </c>
       <c r="U38" s="6" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>3900</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7607,7 @@
       </c>
       <c r="U39" s="6" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4100</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7619,7 @@
       </c>
       <c r="U40" s="6" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4110</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7631,7 @@
       </c>
       <c r="U41" s="6" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4120</t>
         </is>
       </c>
     </row>
@@ -7475,7 +7643,7 @@
       </c>
       <c r="U42" s="6" t="inlineStr">
         <is>
-          <t>4220</t>
+          <t>4200</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7655,7 @@
       </c>
       <c r="U43" s="6" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4210</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7667,7 @@
       </c>
       <c r="U44" s="6" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4220</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7679,7 @@
       </c>
       <c r="U45" s="6" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4230</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7691,7 @@
       </c>
       <c r="U46" s="6" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4240</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7703,7 @@
       </c>
       <c r="U47" s="6" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4300</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7715,7 @@
       </c>
       <c r="U48" s="6" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4310</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7727,7 @@
       </c>
       <c r="U49" s="6" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4400</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7739,7 @@
       </c>
       <c r="U50" s="6" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4500</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7751,7 @@
       </c>
       <c r="U51" s="6" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4600</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7763,7 @@
       </c>
       <c r="U52" s="6" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4610</t>
         </is>
       </c>
     </row>
@@ -7607,7 +7775,7 @@
       </c>
       <c r="U53" s="6" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4700</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7787,7 @@
       </c>
       <c r="U54" s="6" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>4710</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7799,7 @@
       </c>
       <c r="U55" s="6" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>4900</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7811,7 @@
       </c>
       <c r="U56" s="6" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5100</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7823,7 @@
       </c>
       <c r="U57" s="6" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5110</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7835,7 @@
       </c>
       <c r="U58" s="6" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5120</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7847,7 @@
       </c>
       <c r="U59" s="6" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5200</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7859,7 @@
       </c>
       <c r="U60" s="6" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5300</t>
         </is>
       </c>
     </row>
@@ -7703,7 +7871,7 @@
       </c>
       <c r="U61" s="6" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5400</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7883,7 @@
       </c>
       <c r="U62" s="6" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>5500</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7895,7 @@
       </c>
       <c r="U63" s="6" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5510</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7907,7 @@
       </c>
       <c r="U64" s="6" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5600</t>
         </is>
       </c>
     </row>
@@ -7751,7 +7919,7 @@
       </c>
       <c r="U65" s="6" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5610</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7931,7 @@
       </c>
       <c r="U66" s="6" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>5700</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7943,7 @@
       </c>
       <c r="U67" s="6" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5750</t>
         </is>
       </c>
     </row>
@@ -7787,7 +7955,7 @@
       </c>
       <c r="U68" s="6" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5760</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7967,7 @@
       </c>
       <c r="U69" s="6" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5770</t>
         </is>
       </c>
     </row>
@@ -7809,6 +7977,11 @@
           <t>ET</t>
         </is>
       </c>
+      <c r="U70" s="6" t="inlineStr">
+        <is>
+          <t>5800</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="T71" s="6" t="inlineStr">
@@ -7816,6 +7989,11 @@
           <t>FI</t>
         </is>
       </c>
+      <c r="U71" s="6" t="inlineStr">
+        <is>
+          <t>5900</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="T72" s="6" t="inlineStr">
@@ -7823,11 +8001,21 @@
           <t>FJ</t>
         </is>
       </c>
+      <c r="U72" s="6" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="T73" s="6" t="inlineStr">
         <is>
           <t>FK</t>
+        </is>
+      </c>
+      <c r="U73" s="6" t="inlineStr">
+        <is>
+          <t>5930</t>
         </is>
       </c>
     </row>

--- a/docs/migration/almiras-migration-workbook.xlsx
+++ b/docs/migration/almiras-migration-workbook.xlsx
@@ -18,10 +18,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Open payables" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank accounts" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed assets" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERP chart" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bai' ajel contracts" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed assets" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checklist" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERP chart" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="L_yes_no">'Lists'!$A$2:$A$3</definedName>
@@ -566,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -852,94 +853,106 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Fixed assets: The asset register on the cut-over date, one row per asset (or per category where no detail exists). Cost and accumulated depreciation must equal the Falcon accounts in the trial balance.</t>
+          <t>Bai' ajel contracts: Every employee bai' ajel (deferred-payment sale) contract with a balance on the cut-over date. The amounts still open must equal the employee deferred-sale receivable and the deferred profit in the trial balance.</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>الأصول الثابتة: سجل الأصول في تاريخ التحويل، صف لكل أصل (أو لكل فئة عند عدم توفر التفاصيل). يجب أن تساوي التكلفة ومجمع الاستهلاك حسابات فالكون في ميزان المراجعة.</t>
+          <t>عقود البيع الآجل: كل عقد بيع آجل لموظف عليه رصيد في تاريخ التحويل. يجب أن تساوي المبالغ المتبقية ذمم البيع الآجل للموظفين والأرباح المؤجلة في ميزان المراجعة.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Checklist: who fills each part, who approves it, and the final sign-off.</t>
+          <t>Fixed assets: The asset register on the cut-over date, one row per asset (or per category where no detail exists). Cost and accumulated depreciation must equal the Falcon accounts in the trial balance.</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>قائمة التحقق: من يعبئ كل جزء ومن يعتمده والتوقيع النهائي.</t>
+          <t>الأصول الثابتة: سجل الأصول في تاريخ التحويل، صف لكل أصل (أو لكل فئة عند عدم توفر التفاصيل). يجب أن تساوي التكلفة ومجمع الاستهلاك حسابات فالكون في ميزان المراجعة.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>ERP chart: the group chart of accounts in the ERP, for the Account mapping sheet (reference only).</t>
+          <t>Checklist: who fills each part, who approves it, and the final sign-off.</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>دليل حسابات النظام: دليل حسابات المجموعة في النظام، لورقة ربط الحسابات (للاطلاع فقط).</t>
+          <t>قائمة التحقق: من يعبئ كل جزء ومن يعتمده والتوقيع النهائي.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>ERP chart: the group chart of accounts in the ERP, for the Account mapping sheet (reference only).</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>دليل حسابات النظام: دليل حسابات المجموعة في النظام، لورقة ربط الحسابات (للاطلاع فقط).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>Lists: the values of the dropdowns (reference only).</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>القوائم: قيم القوائم المنسدلة (للاطلاع فقط).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Rules the ERP checks</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>القواعد التي يفحصها النظام</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>The trial balance of each entity balances to the halala; every account with a balance is mapped to an ERP account; open receivables and payables equal the customer and vendor accounts; bank book balances, fixed assets and the end-of-service provision equal their accounts in the trial balance.</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>يتوازن ميزان المراجعة لكل كيان حتى الهللة؛ وكل حساب له رصيد مربوط بحساب في النظام؛ وتساوي الذمم المدينة والدائنة المفتوحة حسابات العملاء والموردين؛ وتساوي الأرصدة الدفترية للبنوك والأصول الثابتة ومخصص نهاية الخدمة حساباتها في ميزان المراجعة.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Next steps</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>الخطوات التالية</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Fill → validate (migration_workbook_check) → approve the account mapping (second person) → load drafts → second person posts → tie-out report signed off. See docs/migration/README.md.</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>التعبئة ← الفحص (migration_workbook_check) ← اعتماد ربط الحسابات (شخص آخر) ← تحميل المسودات ← الترحيل بواسطة شخص آخر ← توقيع تقرير المطابقة. انظر docs/migration/README.md.</t>
         </is>
@@ -2098,6 +2111,385 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="6" min="1" max="1"/>
+    <col width="14" customWidth="1" style="6" min="2" max="2"/>
+    <col width="14" customWidth="1" style="6" min="3" max="3"/>
+    <col width="26" customWidth="1" style="6" min="4" max="4"/>
+    <col width="26" customWidth="1" style="6" min="5" max="5"/>
+    <col width="13" customWidth="1" style="7" min="6" max="6"/>
+    <col width="16" customWidth="1" style="15" min="7" max="7"/>
+    <col width="16" customWidth="1" style="15" min="8" max="8"/>
+    <col width="16" customWidth="1" style="15" min="9" max="9"/>
+    <col width="10" customWidth="1" style="17" min="10" max="10"/>
+    <col width="16" customWidth="1" style="15" min="11" max="11"/>
+    <col width="12" customWidth="1" style="6" min="12" max="12"/>
+    <col width="22" customWidth="1" style="6" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bai' ajel contracts / عقود البيع الآجل</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Every employee bai' ajel (deferred-payment sale) contract with a balance on the cut-over date. The amounts still open must equal the employee deferred-sale receivable and the deferred profit in the trial balance.  * = required  [PD] = personal data  Grey rows from row 6 are fake examples: delete them. Do not change rows 1-5.
+كل عقد بيع آجل لموظف عليه رصيد في تاريخ التحويل. يجب أن تساوي المبالغ المتبقية ذمم البيع الآجل للموظفين والأرباح المؤجلة في ميزان المراجعة.  * = مطلوب  [PD] = بيانات شخصية  الصفوف الرمادية من الصف 6 أمثلة وهمية: احذفها. لا تغيّر الصفوف 1-5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Entity code *</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Contract number (legacy) *</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Employee number (as on the Employees sheet) *</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Asset sold (Arabic) *</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Asset sold (English)</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Sale date *</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Sale price (cost + profit, SAR, before VAT) *</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Fixed profit in the price (SAR) *</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>VAT charged to the employee (SAR)</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Number of instalments (whole contract) *</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
+          <t>Paid up to the cut-over (SAR, of price + VAT) *</t>
+        </is>
+      </c>
+      <c r="L3" s="8" t="inlineStr">
+        <is>
+          <t>First instalment after the cut-over (YYYY-MM) *</t>
+        </is>
+      </c>
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>Signed salary-deduction consent (reference)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>رمز الكيان *</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>رقم العقد (السابق) *</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>الرقم الوظيفي (كما في ورقة الموظفين) *</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>الأصل المبيع (بالعربية) *</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>الأصل المبيع (بالإنجليزية)</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>تاريخ البيع *</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>ثمن البيع (التكلفة + الربح، ريال، قبل الضريبة) *</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>الربح الثابت ضمن الثمن (ريال) *</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>الضريبة المحملة على الموظف (ريال)</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>عدد الأقساط (للعقد كله) *</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>المسدد حتى تاريخ التحويل (ريال، من الثمن والضريبة) *</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>أول قسط بعد تاريخ التحويل (سنة-شهر) *</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>مرجع الموافقة الموقعة على الاستقطاع</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>contract_no</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>employee_no</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>asset_description_ar</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>asset_description_en</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>sale_date</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>sale_price</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>profit_amount</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>vat_amount</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>instalments</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>paid_to_date</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>next_instalment_period</t>
+        </is>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>consent_ref</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>EXA</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>EX-BAJ-01</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>EX-001</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>سيارة مثال</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Example car</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>45672</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J6" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>44083.33</v>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>EX-CONSENT-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>EXA</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>EX-BAJ-02</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>EX-002</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>أثاث مثال</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Example furniture</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>46174</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="J7" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>6900</v>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>2027-01</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
+  </mergeCells>
+  <dataValidations count="7">
+    <dataValidation sqref="A6:A2005" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the list" error="Add the entity on the Entities sheet first. / أضف الكيان في ورقة الكيانات أولًا." promptTitle="Entity code" prompt="Entity code * / رمز الكيان *" type="list" errorStyle="warning">
+      <formula1>L_entity</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6:F2005" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Date" error="A date, e.g. 2026-12-31. / تاريخ، مثل 2026-12-31." promptTitle="Sale date" prompt="Sale date * / تاريخ البيع *" type="date" operator="between">
+      <formula1>DATE(1950,1,1)</formula1>
+      <formula2>DATE(2100,12,31)</formula2>
+    </dataValidation>
+    <dataValidation sqref="G6:G2005" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Amount" error="SAR, 0 or more, two decimals at most. / بالريال، صفر أو أكثر، بخانتين عشريتين كحد أقصى." promptTitle="Sale price (cost + profit, SAR, " prompt="Sale price (cost + profit, SAR, before VAT) * / ثمن البيع (التكلفة + الربح، ريال، قبل الضريبة) *" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H6:H2005" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Amount" error="SAR, 0 or more, two decimals at most. / بالريال، صفر أو أكثر، بخانتين عشريتين كحد أقصى." promptTitle="Fixed profit in the price (SAR)" prompt="Fixed profit in the price (SAR) * / الربح الثابت ضمن الثمن (ريال) *" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="I6:I2005" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Amount" error="SAR, 0 or more, two decimals at most. / بالريال، صفر أو أكثر، بخانتين عشريتين كحد أقصى." promptTitle="VAT charged to the employee (SAR" prompt="VAT charged to the employee (SAR) / الضريبة المحملة على الموظف (ريال)" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J6:J2005" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Whole number" error="A whole number of 0 or more. / عدد صحيح يساوي صفرًا أو أكثر." promptTitle="Number of instalments (whole con" prompt="Number of instalments (whole contract) * / عدد الأقساط (للعقد كله) *" type="whole" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="K6:K2005" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Amount" error="SAR, 0 or more, two decimals at most. / بالريال، صفر أو أكثر، بخانتين عشريتين كحد أقصى." promptTitle="Paid up to the cut-over (SAR, of" prompt="Paid up to the cut-over (SAR, of price + VAT) * / المسدد حتى تاريخ التحويل (ريال، من الثمن والضريبة) *" type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2614,13 +3006,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2960,17 +3352,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Fixed asset register entered; ties to cost and depreciation</t>
+          <t>Bai' ajel contracts entered; tie to 1240 and 1241</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>إدخال سجل الأصول الثابتة ومطابقته</t>
+          <t>إدخال عقود البيع الآجل ومطابقتها مع 1240 و1241</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Accountant / المحاسب</t>
+          <t>Payroll officer / مسؤول الرواتب</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -2986,12 +3378,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Validation run: no errors; every warning decided</t>
+          <t>Fixed asset register entered; ties to cost and depreciation</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>تشغيل الفحص: لا أخطاء، وقرار في كل تنبيه</t>
+          <t>إدخال سجل الأصول الثابتة ومطابقته</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -3012,12 +3404,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Opening drafts loaded in the ERP (dry run first)</t>
+          <t>Validation run: no errors; every warning decided</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>تحميل المسودات الافتتاحية في النظام (بتجربة أولًا)</t>
+          <t>تشغيل الفحص: لا أخطاء، وقرار في كل تنبيه</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -3027,7 +3419,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CFO / المدير المالي</t>
         </is>
       </c>
       <c r="G16" s="7" t="n"/>
@@ -3038,17 +3430,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Opening drafts posted by a second person</t>
+          <t>Opening drafts loaded in the ERP (dry run first)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>ترحيل المسودات بواسطة شخص آخر</t>
+          <t>تحميل المسودات الافتتاحية في النظام (بتجربة أولًا)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Approver, not the preparer / المعتمد، وليس المُعد</t>
+          <t>Accountant / المحاسب</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -3064,22 +3456,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Tie-out report: ERP = legacy to the halala, signed</t>
+          <t>Sub-ledgers loaded (open items, banks, employees, provisions, leave, bai' ajel); bank accounts and leave approved</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>تقرير المطابقة: النظام = النظام السابق حتى الهللة، موقع</t>
+          <t>تحميل السجلات الفرعية (البنود المفتوحة والبنوك والموظفين والمخصصات والإجازات والبيع الآجل) واعتماد الحسابات البنكية والإجازات</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Accountant / المحاسب</t>
+          <t>Accountant, HR, payroll / المحاسب والموارد البشرية والرواتب</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>CFO and CEO / المدير المالي والرئيس التنفيذي</t>
+          <t>Approver / المعتمد</t>
         </is>
       </c>
       <c r="G18" s="7" t="n"/>
@@ -3090,71 +3482,123 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>Opening drafts posted by a second person</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>ترحيل المسودات بواسطة شخص آخر</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Approver, not the preparer / المعتمد، وليس المُعد</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Tie-out report: ERP = legacy to the halala, signed</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>تقرير المطابقة: النظام = النظام السابق حتى الهللة، موقع</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Accountant / المحاسب</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>CFO and CEO / المدير المالي والرئيس التنفيذي</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>Filled workbook archived securely; working copies deleted</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>حفظ الملف المعبأ بأمان وحذف النسخ المؤقتة</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Accountant / المحاسب</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Internal audit / المراجعة الداخلية</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="27" t="inlineStr">
+      <c r="G21" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>Sign-off of the tie-out report / اعتماد تقرير المطابقة</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="28" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>Role / الدور</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>Name / الاسم</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>Date / التاريخ</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>Signature / التوقيع</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Prepared by / أعده</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Reviewed by / راجعه</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Prepared by / أعده</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Reviewed by / راجعه</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Approved by (CEO / authorised person) / اعتمده (الرئيس التنفيذي أو المفوض)</t>
         </is>
@@ -3165,7 +3609,7 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="I6:I19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I6:I21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>L_checklist_status</formula1>
     </dataValidation>
   </dataValidations>
@@ -3173,7 +3617,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6576,7 +7020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/migration/almiras-migration-workbook.xlsx
+++ b/docs/migration/almiras-migration-workbook.xlsx
@@ -853,12 +853,12 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Bai' ajel contracts: Every employee bai' ajel (deferred-payment sale) contract with a balance on the cut-over date. The amounts still open must equal the employee deferred-sale receivable and the deferred profit in the trial balance.</t>
+          <t>Bai' ajel contracts: Every employee bai' ajel (deferred-payment sale) contract with a balance on the cut-over date. The amounts still open must equal the employee deferred-sale receivable and the deferred profit in the trial balance. Without the signed consent reference the contract loads with its salary deductions held until payroll records the consent.</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>عقود البيع الآجل: كل عقد بيع آجل لموظف عليه رصيد في تاريخ التحويل. يجب أن تساوي المبالغ المتبقية ذمم البيع الآجل للموظفين والأرباح المؤجلة في ميزان المراجعة.</t>
+          <t>عقود البيع الآجل: كل عقد بيع آجل لموظف عليه رصيد في تاريخ التحويل. يجب أن تساوي المبالغ المتبقية ذمم البيع الآجل للموظفين والأرباح المؤجلة في ميزان المراجعة. وبلا مرجع الموافقة الموقعة يُحمَّل العقد مع إيقاف استقطاعه من الراتب حتى تسجل الرواتب الموافقة.</t>
         </is>
       </c>
     </row>
@@ -2139,8 +2139,8 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Every employee bai' ajel (deferred-payment sale) contract with a balance on the cut-over date. The amounts still open must equal the employee deferred-sale receivable and the deferred profit in the trial balance.  * = required  [PD] = personal data  Grey rows from row 6 are fake examples: delete them. Do not change rows 1-5.
-كل عقد بيع آجل لموظف عليه رصيد في تاريخ التحويل. يجب أن تساوي المبالغ المتبقية ذمم البيع الآجل للموظفين والأرباح المؤجلة في ميزان المراجعة.  * = مطلوب  [PD] = بيانات شخصية  الصفوف الرمادية من الصف 6 أمثلة وهمية: احذفها. لا تغيّر الصفوف 1-5.</t>
+          <t>Every employee bai' ajel (deferred-payment sale) contract with a balance on the cut-over date. The amounts still open must equal the employee deferred-sale receivable and the deferred profit in the trial balance. Without the signed consent reference the contract loads with its salary deductions held until payroll records the consent.  * = required  [PD] = personal data  Grey rows from row 6 are fake examples: delete them. Do not change rows 1-5.
+كل عقد بيع آجل لموظف عليه رصيد في تاريخ التحويل. يجب أن تساوي المبالغ المتبقية ذمم البيع الآجل للموظفين والأرباح المؤجلة في ميزان المراجعة. وبلا مرجع الموافقة الموقعة يُحمَّل العقد مع إيقاف استقطاعه من الراتب حتى تسجل الرواتب الموافقة.  * = مطلوب  [PD] = بيانات شخصية  الصفوف الرمادية من الصف 6 أمثلة وهمية: احذفها. لا تغيّر الصفوف 1-5.</t>
         </is>
       </c>
     </row>
